--- a/mex_match_results.xlsx
+++ b/mex_match_results.xlsx
@@ -1457,12 +1457,12 @@
     <t>Charles Terrazas</t>
   </si>
   <si>
+    <t>Brian Gonzalez</t>
+  </si>
+  <si>
     <t>Vicente Arce</t>
   </si>
   <si>
-    <t>Brian Gonzalez</t>
-  </si>
-  <si>
     <t>Erick Miranda</t>
   </si>
   <si>
@@ -1646,12 +1646,12 @@
     <t>https://fbref.com/en/matches/e3cc6664/Mazatlan-Atletico-January-12-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5f787ed2/Tijuana-America-January-13-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/012864cd/Cruz-Azul-Pachuca-January-13-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5f787ed2/Tijuana-America-January-13-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6f5ab25f/Guadalajara-Santos-Laguna-January-13-2024-Liga-MX</t>
   </si>
   <si>
@@ -1694,12 +1694,12 @@
     <t>https://fbref.com/en/matches/e15c1a07/Monterrey-Santos-Laguna-November-8-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d17bb5e2/Queretaro-Santos-Laguna-March-1-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0ba3c159/Atletico-Puebla-March-1-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d17bb5e2/Queretaro-Santos-Laguna-March-1-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4973734a/Mazatlan-Necaxa-March-1-2024-Liga-MX</t>
   </si>
   <si>
@@ -1715,12 +1715,12 @@
     <t>https://fbref.com/en/matches/24bded1f/Atlas-America-March-2-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/db8b6c40/Tijuana-Leon-March-3-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3d9b464b/Monterrey-Pumas-UNAM-March-3-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/db8b6c40/Tijuana-Leon-March-3-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/5362c2ef/Guadalajara-Mazatlan-September-26-2023-Liga-MX</t>
   </si>
   <si>
@@ -1730,18 +1730,18 @@
     <t>https://fbref.com/en/matches/2165d0d0/America-Pachuca-October-3-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/35a78eee/Necaxa-Cruz-Azul-October-4-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/031cb346/Pumas-UNAM-Queretaro-October-4-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/35a78eee/Necaxa-Cruz-Azul-October-4-2023-Liga-MX</t>
+    <t>https://fbref.com/en/matches/3d4ca1d4/UANL-Toluca-October-4-2023-Liga-MX</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1f0d0da7/Santos-Laguna-Tijuana-October-4-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d4ca1d4/UANL-Toluca-October-4-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9095b36f/Leon-Atlas-October-24-2023-Liga-MX</t>
   </si>
   <si>
@@ -1823,12 +1823,12 @@
     <t>https://fbref.com/en/matches/3cdd0016/Atlas-Monterrey-March-17-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e5e1618e/Toluca-Pumas-UNAM-March-17-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c58f665b/Atletico-Pachuca-March-17-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e5e1618e/Toluca-Pumas-UNAM-March-17-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c05d8fe8/FC-Juarez-Pachuca-October-20-2023-Liga-MX</t>
   </si>
   <si>
@@ -1865,12 +1865,12 @@
     <t>https://fbref.com/en/matches/82fb0906/America-Atletico-March-29-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cf6f17d9/Pachuca-Toluca-March-30-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7e8a1562/Monterrey-Guadalajara-March-30-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cf6f17d9/Pachuca-Toluca-March-30-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d4fde25d/Pumas-UNAM-Cruz-Azul-March-30-2024-Liga-MX</t>
   </si>
   <si>
@@ -1943,12 +1943,12 @@
     <t>https://fbref.com/en/matches/378e5ac6/Queretaro-Guadalajara-October-31-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7407560a/Leon-Pumas-UNAM-October-31-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5ce71d69/Monterrey-Necaxa-October-31-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7407560a/Leon-Pumas-UNAM-October-31-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0e41aef6/Cruz-Azul-FC-Juarez-November-1-2023-Liga-MX</t>
   </si>
   <si>
@@ -1982,12 +1982,12 @@
     <t>https://fbref.com/en/matches/d2097b1b/Monterrey-UANL-April-13-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f7d68a7c/Pumas-UNAM-Leon-April-14-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a6eae94e/Atlas-Atletico-April-14-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f7d68a7c/Pumas-UNAM-Leon-April-14-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e7f6b1f5/FC-Juarez-Tijuana-April-14-2024-Liga-MX</t>
   </si>
   <si>
@@ -2033,12 +2033,12 @@
     <t>https://fbref.com/en/matches/590dce39/UANL-Necaxa-April-20-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b8055aa6/Santos-Laguna-Pachuca-April-20-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/746e5777/Guadalajara-Queretaro-April-20-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b8055aa6/Santos-Laguna-Pachuca-April-20-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2c78241f/Pumas-UNAM-America-April-20-2024-Liga-MX</t>
   </si>
   <si>
@@ -2054,12 +2054,12 @@
     <t>https://fbref.com/en/matches/8e6e9b85/Tijuana-Pachuca-November-10-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fa4c796c/Atletico-Santos-Laguna-November-11-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/540232e3/Queretaro-Monterrey-November-11-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fa4c796c/Atletico-Santos-Laguna-November-11-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3e5b65f7/Pumas-UNAM-Guadalajara-November-11-2023-Liga-MX</t>
   </si>
   <si>
@@ -2081,24 +2081,24 @@
     <t>https://fbref.com/en/matches/066f8e02/FC-Juarez-Leon-April-27-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ca622d65/UANL-Tijuana-April-27-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c5197c83/Toluca-Cruz-Azul-April-27-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ca622d65/UANL-Tijuana-April-27-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1727c3c4/Pachuca-Mazatlan-April-27-2024-Liga-MX</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2fb3c3e0/Atlas-Guadalajara-April-27-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/55754ab7/Santos-Laguna-Atletico-April-28-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4136ce8b/Necaxa-Monterrey-April-28-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/55754ab7/Santos-Laguna-Atletico-April-28-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f682eb2b/Puebla-Santos-Laguna-July-7-2023-Liga-MX</t>
   </si>
   <si>
@@ -2186,12 +2186,12 @@
     <t>https://fbref.com/en/matches/fbc30bce/Puebla-Toluca-January-26-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9787800b/Leon-Santos-Laguna-January-27-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0d3de91a/Cruz-Azul-Mazatlan-January-27-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9787800b/Leon-Santos-Laguna-January-27-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0533da8c/Monterrey-Atletico-January-27-2024-Liga-MX</t>
   </si>
   <si>
@@ -2225,21 +2225,21 @@
     <t>https://fbref.com/en/matches/7b6538c4/Queretaro-Pachuca-August-20-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/79c2aa6a/Necaxa-UANL-August-20-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4e9d84a2/America-Atlas-August-20-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/79c2aa6a/Necaxa-UANL-August-20-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/00b81bcb/Monterrey-Tijuana-October-25-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8d0be42a/Atletico-UANL-January-24-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/58a0b02c/Monterrey-Queretaro-January-24-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8d0be42a/Atletico-UANL-January-24-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fdbb9d04/FC-Juarez-America-January-24-2024-Liga-MX</t>
   </si>
   <si>
@@ -2360,12 +2360,12 @@
     <t>https://fbref.com/en/matches/ef8a5ea5/Cruz-Azul-Atletico-February-10-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/818ef662/Santos-Laguna-UANL-February-10-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2681bdd7/Monterrey-Pachuca-February-10-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/818ef662/Santos-Laguna-UANL-February-10-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a0f496c6/Pumas-UNAM-Puebla-February-11-2024-Liga-MX</t>
   </si>
   <si>
@@ -2486,12 +2486,12 @@
     <t>https://fbref.com/en/matches/78ceb5ac/Puebla-Pumas-UNAM-September-22-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e28dfbe1/Leon-Tijuana-September-23-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b550b761/Guadalajara-Pachuca-September-23-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e28dfbe1/Leon-Tijuana-September-23-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d3c7c413/UANL-Monterrey-September-23-2023-Liga-MX</t>
   </si>
   <si>
@@ -2525,10 +2525,10 @@
     <t>https://fbref.com/en/matches/9fc26aa2/Queretaro-Atletico-February-27-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e9f9b822/UANL-FC-Juarez-February-28-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/df4574ac/Tijuana-Monterrey-February-28-2024-Liga-MX</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e9f9b822/UANL-FC-Juarez-February-28-2024-Liga-MX</t>
   </si>
 </sst>
 </file>
@@ -5600,31 +5600,31 @@
         <v>385</v>
       </c>
       <c r="K47" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L47" t="n">
         <v>0.0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="N47" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O47" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>26100.0</v>
+        <v>31133.0</v>
       </c>
       <c r="R47" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="S47" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="T47" t="s">
         <v>377</v>
@@ -5665,31 +5665,31 @@
         <v>385</v>
       </c>
       <c r="K48" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L48" t="n">
         <v>0.0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="N48" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="O48" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>31133.0</v>
+        <v>26100.0</v>
       </c>
       <c r="R48" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S48" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="T48" t="s">
         <v>377</v>
@@ -6640,28 +6640,28 @@
         <v>385</v>
       </c>
       <c r="K63" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="L63" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M63" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="N63" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="O63" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>12581.0</v>
+        <v>12004.0</v>
       </c>
       <c r="R63" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="S63" t="s">
         <v>481</v>
@@ -6705,28 +6705,28 @@
         <v>385</v>
       </c>
       <c r="K64" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="L64" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N64" t="s">
+        <v>426</v>
+      </c>
+      <c r="O64" t="n">
         <v>0.0</v>
       </c>
-      <c r="M64" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N64" t="s">
-        <v>424</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.0</v>
-      </c>
       <c r="P64" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>12004.0</v>
+        <v>12581.0</v>
       </c>
       <c r="R64" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="S64" t="s">
         <v>482</v>
@@ -7095,31 +7095,31 @@
         <v>385</v>
       </c>
       <c r="K70" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L70" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="N70" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="O70" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>47090.0</v>
+        <v>17333.0</v>
       </c>
       <c r="R70" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="S70" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="T70" t="s">
         <v>377</v>
@@ -7160,31 +7160,31 @@
         <v>385</v>
       </c>
       <c r="K71" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="L71" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="N71" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q71" t="n">
-        <v>17333.0</v>
+        <v>47090.0</v>
       </c>
       <c r="R71" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="S71" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="T71" t="s">
         <v>377</v>
@@ -7420,31 +7420,31 @@
         <v>393</v>
       </c>
       <c r="K75" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L75" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M75" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="N75" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q75" t="n">
-        <v>8074.0</v>
+        <v>10923.0</v>
       </c>
       <c r="R75" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="S75" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="T75" t="s">
         <v>377</v>
@@ -7485,31 +7485,31 @@
         <v>393</v>
       </c>
       <c r="K76" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L76" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="M76" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N76" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="O76" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>10923.0</v>
+        <v>8074.0</v>
       </c>
       <c r="R76" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="S76" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="T76" t="s">
         <v>377</v>
@@ -7550,31 +7550,31 @@
         <v>400</v>
       </c>
       <c r="K77" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="L77" t="n">
         <v>2.0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="N77" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="O77" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.0</v>
+        <v>1.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>7038.0</v>
+        <v>37117.0</v>
       </c>
       <c r="R77" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="S77" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="T77" t="s">
         <v>377</v>
@@ -7615,31 +7615,31 @@
         <v>400</v>
       </c>
       <c r="K78" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="L78" t="n">
         <v>2.0</v>
       </c>
       <c r="M78" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="N78" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O78" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P78" t="n">
         <v>2.0</v>
       </c>
-      <c r="P78" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Q78" t="n">
-        <v>37117.0</v>
+        <v>7038.0</v>
       </c>
       <c r="R78" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="S78" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="T78" t="s">
         <v>377</v>
@@ -9435,31 +9435,31 @@
         <v>385</v>
       </c>
       <c r="K106" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="L106" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M106" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P106" t="n">
         <v>0.6</v>
       </c>
       <c r="Q106" t="n">
-        <v>15634.0</v>
+        <v>27273.0</v>
       </c>
       <c r="R106" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="S106" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="T106" t="s">
         <v>377</v>
@@ -9500,31 +9500,31 @@
         <v>385</v>
       </c>
       <c r="K107" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="L107" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="N107" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P107" t="n">
         <v>0.6</v>
       </c>
       <c r="Q107" t="n">
-        <v>27273.0</v>
+        <v>15634.0</v>
       </c>
       <c r="R107" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="S107" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="T107" t="s">
         <v>377</v>
@@ -10345,31 +10345,31 @@
         <v>385</v>
       </c>
       <c r="K120" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L120" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M120" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N120" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="O120" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="P120" t="n">
-        <v>1.0</v>
+        <v>1.6</v>
       </c>
       <c r="Q120" t="n">
-        <v>46165.0</v>
+        <v>20059.0</v>
       </c>
       <c r="R120" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="S120" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="T120" t="s">
         <v>377</v>
@@ -10410,31 +10410,31 @@
         <v>385</v>
       </c>
       <c r="K121" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L121" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N121" t="s">
+        <v>427</v>
+      </c>
+      <c r="O121" t="n">
         <v>2.0</v>
       </c>
-      <c r="M121" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N121" t="s">
-        <v>434</v>
-      </c>
-      <c r="O121" t="n">
-        <v>3.0</v>
-      </c>
       <c r="P121" t="n">
-        <v>1.6</v>
+        <v>1.0</v>
       </c>
       <c r="Q121" t="n">
-        <v>20059.0</v>
+        <v>46165.0</v>
       </c>
       <c r="R121" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="S121" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T121" t="s">
         <v>377</v>
@@ -10889,7 +10889,7 @@
         <v>446</v>
       </c>
       <c r="S128" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T128" t="s">
         <v>377</v>
@@ -12035,31 +12035,31 @@
         <v>386</v>
       </c>
       <c r="K146" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L146" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="M146" t="n">
-        <v>1.0</v>
+        <v>1.3</v>
       </c>
       <c r="N146" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="O146" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P146" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q146" t="n">
-        <v>25292.0</v>
+        <v>22898.0</v>
       </c>
       <c r="R146" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="S146" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="T146" t="s">
         <v>377</v>
@@ -12100,31 +12100,31 @@
         <v>386</v>
       </c>
       <c r="K147" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="M147" t="n">
-        <v>1.3</v>
+        <v>1.0</v>
       </c>
       <c r="N147" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O147" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P147" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q147" t="n">
-        <v>22898.0</v>
+        <v>25292.0</v>
       </c>
       <c r="R147" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="S147" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="T147" t="s">
         <v>377</v>
@@ -12880,31 +12880,31 @@
         <v>385</v>
       </c>
       <c r="K159" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L159" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M159" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O159" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P159" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q159" t="n">
-        <v>10750.0</v>
+        <v>23127.0</v>
       </c>
       <c r="R159" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="S159" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="T159" t="s">
         <v>377</v>
@@ -12945,31 +12945,31 @@
         <v>385</v>
       </c>
       <c r="K160" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L160" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M160" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="N160" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="O160" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P160" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q160" t="n">
-        <v>23127.0</v>
+        <v>10750.0</v>
       </c>
       <c r="R160" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="S160" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="T160" t="s">
         <v>377</v>
@@ -13985,31 +13985,31 @@
         <v>397</v>
       </c>
       <c r="K176" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L176" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N176" t="s">
+        <v>433</v>
+      </c>
+      <c r="O176" t="n">
         <v>2.0</v>
       </c>
-      <c r="M176" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N176" t="s">
-        <v>439</v>
-      </c>
-      <c r="O176" t="n">
-        <v>0.0</v>
-      </c>
       <c r="P176" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q176" t="n">
-        <v>37040.0</v>
+        <v>10309.0</v>
       </c>
       <c r="R176" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="S176" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="T176" t="s">
         <v>377</v>
@@ -14050,31 +14050,31 @@
         <v>397</v>
       </c>
       <c r="K177" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L177" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N177" t="s">
+        <v>439</v>
+      </c>
+      <c r="O177" t="n">
         <v>0.0</v>
       </c>
-      <c r="M177" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N177" t="s">
-        <v>433</v>
-      </c>
-      <c r="O177" t="n">
-        <v>2.0</v>
-      </c>
       <c r="P177" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="Q177" t="n">
-        <v>10309.0</v>
+        <v>37040.0</v>
       </c>
       <c r="R177" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="S177" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="T177" t="s">
         <v>377</v>
@@ -14440,31 +14440,31 @@
         <v>407</v>
       </c>
       <c r="K183" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="L183" t="n">
         <v>0.0</v>
       </c>
       <c r="M183" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N183" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="O183" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P183" t="n">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="Q183" t="n">
-        <v>16717.0</v>
+        <v>14479.0</v>
       </c>
       <c r="R183" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="S183" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="T183" t="s">
         <v>377</v>
@@ -14505,31 +14505,31 @@
         <v>407</v>
       </c>
       <c r="K184" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="L184" t="n">
         <v>0.0</v>
       </c>
       <c r="M184" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="N184" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="O184" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="P184" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="Q184" t="n">
-        <v>14479.0</v>
+        <v>16717.0</v>
       </c>
       <c r="R184" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="S184" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="T184" t="s">
         <v>377</v>
@@ -15025,16 +15025,16 @@
         <v>393</v>
       </c>
       <c r="K192" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="M192" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="N192" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O192" t="n">
         <v>1.0</v>
@@ -15043,13 +15043,13 @@
         <v>0.8</v>
       </c>
       <c r="Q192" t="n">
-        <v>27273.0</v>
+        <v>39459.0</v>
       </c>
       <c r="R192" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="S192" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="T192" t="s">
         <v>377</v>
@@ -15090,16 +15090,16 @@
         <v>393</v>
       </c>
       <c r="K193" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L193" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="N193" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O193" t="n">
         <v>1.0</v>
@@ -15108,13 +15108,13 @@
         <v>0.8</v>
       </c>
       <c r="Q193" t="n">
-        <v>39459.0</v>
+        <v>27273.0</v>
       </c>
       <c r="R193" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S193" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="T193" t="s">
         <v>377</v>
@@ -15285,31 +15285,31 @@
         <v>385</v>
       </c>
       <c r="K196" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="L196" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M196" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N196" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="O196" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="P196" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q196" t="n">
-        <v>19388.0</v>
+        <v>16422.0</v>
       </c>
       <c r="R196" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="S196" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="T196" t="s">
         <v>377</v>
@@ -15350,31 +15350,31 @@
         <v>385</v>
       </c>
       <c r="K197" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="L197" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="M197" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N197" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="O197" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="P197" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q197" t="n">
-        <v>16422.0</v>
+        <v>19388.0</v>
       </c>
       <c r="R197" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="S197" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="T197" t="s">
         <v>377</v>
@@ -15439,7 +15439,7 @@
         <v>444</v>
       </c>
       <c r="S198" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T198" t="s">
         <v>377</v>
@@ -16024,7 +16024,7 @@
         <v>444</v>
       </c>
       <c r="S207" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T207" t="s">
         <v>377</v>
@@ -16739,7 +16739,7 @@
         <v>456</v>
       </c>
       <c r="S218" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T218" t="s">
         <v>377</v>
@@ -17194,7 +17194,7 @@
         <v>457</v>
       </c>
       <c r="S225" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T225" t="s">
         <v>377</v>
@@ -17300,31 +17300,31 @@
         <v>407</v>
       </c>
       <c r="K227" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="L227" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N227" t="s">
+        <v>424</v>
+      </c>
+      <c r="O227" t="n">
         <v>2.0</v>
       </c>
-      <c r="M227" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N227" t="s">
-        <v>436</v>
-      </c>
-      <c r="O227" t="n">
-        <v>1.0</v>
-      </c>
       <c r="P227" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q227" t="n">
-        <v>20032.0</v>
+        <v>18271.0</v>
       </c>
       <c r="R227" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="S227" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="T227" t="s">
         <v>377</v>
@@ -17365,31 +17365,31 @@
         <v>407</v>
       </c>
       <c r="K228" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="L228" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M228" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="N228" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="O228" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P228" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q228" t="n">
-        <v>18271.0</v>
+        <v>20032.0</v>
       </c>
       <c r="R228" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="S228" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="T228" t="s">
         <v>377</v>
@@ -18104,7 +18104,7 @@
         <v>460</v>
       </c>
       <c r="S239" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T239" t="s">
         <v>377</v>
@@ -18145,31 +18145,31 @@
         <v>399</v>
       </c>
       <c r="K240" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L240" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M240" t="n">
-        <v>1.8</v>
+        <v>1.0</v>
       </c>
       <c r="N240" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="O240" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="P240" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q240" t="n">
-        <v>17046.0</v>
+        <v>13585.0</v>
       </c>
       <c r="R240" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="S240" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="T240" t="s">
         <v>377</v>
@@ -18210,31 +18210,31 @@
         <v>399</v>
       </c>
       <c r="K241" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L241" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M241" t="n">
-        <v>1.0</v>
+        <v>1.8</v>
       </c>
       <c r="N241" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="O241" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="P241" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q241" t="n">
-        <v>13585.0</v>
+        <v>17046.0</v>
       </c>
       <c r="R241" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="S241" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="T241" t="s">
         <v>377</v>
@@ -18340,31 +18340,31 @@
         <v>385</v>
       </c>
       <c r="K243" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="L243" t="n">
         <v>1.0</v>
       </c>
       <c r="M243" t="n">
-        <v>1.9</v>
+        <v>1.0</v>
       </c>
       <c r="N243" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="O243" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P243" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q243" t="n">
-        <v>32263.0</v>
+        <v>20089.0</v>
       </c>
       <c r="R243" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="S243" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="T243" t="s">
         <v>377</v>
@@ -18405,31 +18405,31 @@
         <v>385</v>
       </c>
       <c r="K244" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="L244" t="n">
         <v>1.0</v>
       </c>
       <c r="M244" t="n">
-        <v>1.0</v>
+        <v>1.9</v>
       </c>
       <c r="N244" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="O244" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P244" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q244" t="n">
-        <v>20089.0</v>
+        <v>32263.0</v>
       </c>
       <c r="R244" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="S244" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="T244" t="s">
         <v>377</v>
@@ -18689,7 +18689,7 @@
         <v>459</v>
       </c>
       <c r="S248" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T248" t="s">
         <v>377</v>
@@ -20899,7 +20899,7 @@
         <v>445</v>
       </c>
       <c r="S282" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="T282" t="s">
         <v>377</v>
@@ -21070,31 +21070,31 @@
         <v>386</v>
       </c>
       <c r="K285" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="L285" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N285" t="s">
+        <v>431</v>
+      </c>
+      <c r="O285" t="n">
         <v>3.0</v>
       </c>
-      <c r="M285" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N285" t="s">
-        <v>433</v>
-      </c>
-      <c r="O285" t="n">
+      <c r="P285" t="n">
         <v>2.0</v>
       </c>
-      <c r="P285" t="n">
-        <v>0.7</v>
-      </c>
       <c r="Q285" t="n">
-        <v>46211.0</v>
+        <v>15727.0</v>
       </c>
       <c r="R285" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="S285" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T285" t="s">
         <v>377</v>
@@ -21135,31 +21135,31 @@
         <v>386</v>
       </c>
       <c r="K286" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="L286" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="M286" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="N286" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O286" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="P286" t="n">
-        <v>2.0</v>
+        <v>0.7</v>
       </c>
       <c r="Q286" t="n">
-        <v>15727.0</v>
+        <v>46211.0</v>
       </c>
       <c r="R286" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="S286" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="T286" t="s">
         <v>377</v>
@@ -22589,7 +22589,7 @@
         <v>452</v>
       </c>
       <c r="S308" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T308" t="s">
         <v>377</v>
@@ -23800,31 +23800,31 @@
         <v>393</v>
       </c>
       <c r="K327" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L327" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M327" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="N327" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O327" t="n">
         <v>0.0</v>
       </c>
       <c r="P327" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="Q327" t="n">
-        <v>31370.0</v>
+        <v>16428.0</v>
       </c>
       <c r="R327" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="S327" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="T327" t="s">
         <v>377</v>
@@ -23865,31 +23865,31 @@
         <v>393</v>
       </c>
       <c r="K328" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L328" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="M328" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="N328" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="O328" t="n">
         <v>0.0</v>
       </c>
       <c r="P328" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="Q328" t="n">
-        <v>16428.0</v>
+        <v>31370.0</v>
       </c>
       <c r="R328" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="S328" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="T328" t="s">
         <v>377</v>
@@ -24344,7 +24344,7 @@
         <v>452</v>
       </c>
       <c r="S335" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T335" t="s">
         <v>377</v>
@@ -24645,31 +24645,31 @@
         <v>385</v>
       </c>
       <c r="K340" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="L340" t="n">
         <v>1.0</v>
       </c>
       <c r="M340" t="n">
-        <v>1.0</v>
+        <v>1.1</v>
       </c>
       <c r="N340" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="O340" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P340" t="n">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="Q340" t="n">
-        <v>18333.0</v>
+        <v>34731.0</v>
       </c>
       <c r="R340" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="S340" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="T340" t="s">
         <v>377</v>
@@ -24710,31 +24710,31 @@
         <v>385</v>
       </c>
       <c r="K341" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L341" t="n">
         <v>1.0</v>
       </c>
       <c r="M341" t="n">
-        <v>1.1</v>
+        <v>1.0</v>
       </c>
       <c r="N341" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="O341" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P341" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="Q341" t="n">
-        <v>34731.0</v>
+        <v>18333.0</v>
       </c>
       <c r="R341" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="S341" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="T341" t="s">
         <v>377</v>
